--- a/Current TAPPs/Lab-XCT_TAPP_v38.xlsx
+++ b/Current TAPPs/Lab-XCT_TAPP_v38.xlsx
@@ -13145,7 +13145,7 @@
       </c>
       <c r="B17" s="1" t="inlineStr">
         <is>
-          <t>Choose a listed value AND qualify it in the same cell — the detail is expected, not optional. Typically what was corrected, which analytes or phases it applied to, the method or equation used, or the source it came from. An answer the list cannot express is also valid here.</t>
+          <t>Choose a listed value AND qualify it in the same cell — the detail is expected, not optional. Typically what was corrected, which target species or phases it applied to, the method or equation used, or the source it came from. An answer the list cannot express is also valid here.</t>
         </is>
       </c>
     </row>
